--- a/public/collegePortalExcel/collegePortal-test1.xlsx
+++ b/public/collegePortalExcel/collegePortal-test1.xlsx
@@ -1,59 +1,755 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9138C931-9BD8-4F3E-A4A0-7C7C0C637584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19368" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Student Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="243">
+  <si>
+    <t>name</t>
+  </si>
   <si>
     <t>email</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>collegeId</t>
-  </si>
-  <si>
-    <t>college</t>
+    <t>password</t>
   </si>
   <si>
     <t>departmentId</t>
   </si>
   <si>
-    <t>facultyId</t>
-  </si>
-  <si>
-    <t>faculty</t>
-  </si>
-  <si>
-    <t>departmentId2</t>
+    <t>personalEmail</t>
+  </si>
+  <si>
+    <t>DOB</t>
+  </si>
+  <si>
+    <t>phoneNo</t>
+  </si>
+  <si>
+    <t>nationality</t>
+  </si>
+  <si>
+    <t>countryCode</t>
+  </si>
+  <si>
+    <t>departmentName</t>
+  </si>
+  <si>
+    <t>Natasha Romanov</t>
+  </si>
+  <si>
+    <t>natashar@example.com</t>
+  </si>
+  <si>
+    <t>blackwidow2024</t>
+  </si>
+  <si>
+    <t>STU1016</t>
+  </si>
+  <si>
+    <t>natasha.r@gmail.com</t>
+  </si>
+  <si>
+    <t>2000-01-07</t>
+  </si>
+  <si>
+    <t>4512369870</t>
+  </si>
+  <si>
+    <t>Russian</t>
+  </si>
+  <si>
+    <t>+7</t>
+  </si>
+  <si>
+    <t>International Relations</t>
+  </si>
+  <si>
+    <t>Hiroshi Tanaka</t>
+  </si>
+  <si>
+    <t>hiroshit@example.com</t>
+  </si>
+  <si>
+    <t>tanaka1234</t>
+  </si>
+  <si>
+    <t>STU1017</t>
+  </si>
+  <si>
+    <t>hiroshi.t@gmail.com</t>
+  </si>
+  <si>
+    <t>1999-12-03</t>
+  </si>
+  <si>
+    <t>8529637410</t>
+  </si>
+  <si>
+    <t>Japanese</t>
+  </si>
+  <si>
+    <t>+81</t>
+  </si>
+  <si>
+    <t>Robotics</t>
+  </si>
+  <si>
+    <t>Fatima Al-Sayed</t>
+  </si>
+  <si>
+    <t>fatimas@example.com</t>
+  </si>
+  <si>
+    <t>fatima2023</t>
+  </si>
+  <si>
+    <t>STU1018</t>
+  </si>
+  <si>
+    <t>fatima.s@gmail.com</t>
+  </si>
+  <si>
+    <t>2001-03-25</t>
+  </si>
+  <si>
+    <t>7539514682</t>
+  </si>
+  <si>
+    <t>Saudi Arabian</t>
+  </si>
+  <si>
+    <t>+966</t>
+  </si>
+  <si>
+    <t>Medicine</t>
+  </si>
+  <si>
+    <t>Lars Johansson</t>
+  </si>
+  <si>
+    <t>larsj@example.com</t>
+  </si>
+  <si>
+    <t>lars2000secure</t>
+  </si>
+  <si>
+    <t>STU1019</t>
+  </si>
+  <si>
+    <t>lars.j@gmail.com</t>
+  </si>
+  <si>
+    <t>2000-07-19</t>
+  </si>
+  <si>
+    <t>1472583690</t>
+  </si>
+  <si>
+    <t>Swedish</t>
+  </si>
+  <si>
+    <t>+46</t>
+  </si>
+  <si>
+    <t>Environmental Science</t>
+  </si>
+  <si>
+    <t>Isabella Martinez</t>
+  </si>
+  <si>
+    <t>isabellam@example.com</t>
+  </si>
+  <si>
+    <t>bella1234</t>
+  </si>
+  <si>
+    <t>STU1020</t>
+  </si>
+  <si>
+    <t>isabella.m@gmail.com</t>
+  </si>
+  <si>
+    <t>2002-05-31</t>
+  </si>
+  <si>
+    <t>3698521470</t>
+  </si>
+  <si>
+    <t>Colombian</t>
+  </si>
+  <si>
+    <t>+57</t>
+  </si>
+  <si>
+    <t>Psychology</t>
+  </si>
+  <si>
+    <t>Raj Gupta</t>
+  </si>
+  <si>
+    <t>rajg@example.com</t>
+  </si>
+  <si>
+    <t>rajgupta2024</t>
+  </si>
+  <si>
+    <t>STU1021</t>
+  </si>
+  <si>
+    <t>raj.gupta@gmail.com</t>
+  </si>
+  <si>
+    <t>1999-09-14</t>
+  </si>
+  <si>
+    <t>9632587410</t>
+  </si>
+  <si>
+    <t>Indian</t>
+  </si>
+  <si>
+    <t>+91</t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>Ananya Sharma</t>
+  </si>
+  <si>
+    <t>ananyas@example.com</t>
+  </si>
+  <si>
+    <t>ananya1998</t>
+  </si>
+  <si>
+    <t>STU1022</t>
+  </si>
+  <si>
+    <t>ananya.s@gmail.com</t>
+  </si>
+  <si>
+    <t>1998-11-27</t>
+  </si>
+  <si>
+    <t>8524169730</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>Mohammed Al-Farsi</t>
+  </si>
+  <si>
+    <t>mohammedf@example.com</t>
+  </si>
+  <si>
+    <t>maf2023secure</t>
+  </si>
+  <si>
+    <t>STU1023</t>
+  </si>
+  <si>
+    <t>mohammed.f@gmail.com</t>
+  </si>
+  <si>
+    <t>2001-08-12</t>
+  </si>
+  <si>
+    <t>7896541230</t>
+  </si>
+  <si>
+    <t>Omani</t>
+  </si>
+  <si>
+    <t>+968</t>
+  </si>
+  <si>
+    <t>Petroleum Engineering</t>
+  </si>
+  <si>
+    <t>Elena Petrova</t>
+  </si>
+  <si>
+    <t>elenap@example.com</t>
+  </si>
+  <si>
+    <t>elena2001</t>
+  </si>
+  <si>
+    <t>STU1024</t>
+  </si>
+  <si>
+    <t>elena.p@gmail.com</t>
+  </si>
+  <si>
+    <t>2001-06-05</t>
+  </si>
+  <si>
+    <t>7539518520</t>
+  </si>
+  <si>
+    <t>Mathematics</t>
+  </si>
+  <si>
+    <t>Gabriel Santos</t>
+  </si>
+  <si>
+    <t>gabriels@example.com</t>
+  </si>
+  <si>
+    <t>gabsantos99</t>
+  </si>
+  <si>
+    <t>STU1025</t>
+  </si>
+  <si>
+    <t>gabriel.s@gmail.com</t>
+  </si>
+  <si>
+    <t>1999-02-18</t>
+  </si>
+  <si>
+    <t>9517538520</t>
+  </si>
+  <si>
+    <t>Brazilian</t>
+  </si>
+  <si>
+    <t>+55</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>Yuna Kim</t>
+  </si>
+  <si>
+    <t>yunak@example.com</t>
+  </si>
+  <si>
+    <t>yunakim2002</t>
+  </si>
+  <si>
+    <t>STU1026</t>
+  </si>
+  <si>
+    <t>yuna.k@gmail.com</t>
+  </si>
+  <si>
+    <t>2002-04-11</t>
+  </si>
+  <si>
+    <t>7845129630</t>
+  </si>
+  <si>
+    <t>Korean</t>
+  </si>
+  <si>
+    <t>+82</t>
+  </si>
+  <si>
+    <t>Fine Arts</t>
+  </si>
+  <si>
+    <t>Aiden O'Connor</t>
+  </si>
+  <si>
+    <t>aideno@example.com</t>
+  </si>
+  <si>
+    <t>aiden2000</t>
+  </si>
+  <si>
+    <t>STU1027</t>
+  </si>
+  <si>
+    <t>aiden.o@gmail.com</t>
+  </si>
+  <si>
+    <t>2000-10-22</t>
+  </si>
+  <si>
+    <t>1598746320</t>
+  </si>
+  <si>
+    <t>Irish</t>
+  </si>
+  <si>
+    <t>+353</t>
+  </si>
+  <si>
+    <t>Literature</t>
+  </si>
+  <si>
+    <t>Leila Mbeki</t>
+  </si>
+  <si>
+    <t>leilam@example.com</t>
+  </si>
+  <si>
+    <t>leila1997</t>
+  </si>
+  <si>
+    <t>STU1028</t>
+  </si>
+  <si>
+    <t>leila.m@gmail.com</t>
+  </si>
+  <si>
+    <t>1997-12-29</t>
+  </si>
+  <si>
+    <t>3698524170</t>
+  </si>
+  <si>
+    <t>South African</t>
+  </si>
+  <si>
+    <t>+27</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Sven Lindgren</t>
+  </si>
+  <si>
+    <t>svenl@example.com</t>
+  </si>
+  <si>
+    <t>sven2001</t>
+  </si>
+  <si>
+    <t>STU1029</t>
+  </si>
+  <si>
+    <t>sven.l@gmail.com</t>
+  </si>
+  <si>
+    <t>2001-07-08</t>
+  </si>
+  <si>
+    <t>1478523690</t>
+  </si>
+  <si>
+    <t>Cheng Wei</t>
+  </si>
+  <si>
+    <t>chengw@example.com</t>
+  </si>
+  <si>
+    <t>cheng1999</t>
+  </si>
+  <si>
+    <t>STU1030</t>
+  </si>
+  <si>
+    <t>cheng.wei@gmail.com</t>
+  </si>
+  <si>
+    <t>1999-04-17</t>
+  </si>
+  <si>
+    <t>9638527410</t>
+  </si>
+  <si>
+    <t>Chinese</t>
+  </si>
+  <si>
+    <t>+86</t>
+  </si>
+  <si>
+    <t>Electrical Engineering</t>
+  </si>
+  <si>
+    <t>Zainab Khalid</t>
+  </si>
+  <si>
+    <t>zainabk@example.com</t>
+  </si>
+  <si>
+    <t>zainab2002</t>
+  </si>
+  <si>
+    <t>STU1031</t>
+  </si>
+  <si>
+    <t>zainab.k@gmail.com</t>
+  </si>
+  <si>
+    <t>2002-03-14</t>
+  </si>
+  <si>
+    <t>7458961230</t>
+  </si>
+  <si>
+    <t>Pakistani</t>
+  </si>
+  <si>
+    <t>+92</t>
+  </si>
+  <si>
+    <t>Economics</t>
+  </si>
+  <si>
+    <t>Maxim Petrov</t>
+  </si>
+  <si>
+    <t>maximp@example.com</t>
+  </si>
+  <si>
+    <t>maxim1998</t>
+  </si>
+  <si>
+    <t>STU1032</t>
+  </si>
+  <si>
+    <t>maxim.p@gmail.com</t>
+  </si>
+  <si>
+    <t>1998-09-30</t>
+  </si>
+  <si>
+    <t>Nuclear Physics</t>
+  </si>
+  <si>
+    <t>Nadia Malik</t>
+  </si>
+  <si>
+    <t>nadiam@example.com</t>
+  </si>
+  <si>
+    <t>nadia2003</t>
+  </si>
+  <si>
+    <t>STU1033</t>
+  </si>
+  <si>
+    <t>nadia.m@gmail.com</t>
+  </si>
+  <si>
+    <t>2003-01-25</t>
+  </si>
+  <si>
+    <t>Egyptian</t>
+  </si>
+  <si>
+    <t>+20</t>
+  </si>
+  <si>
+    <t>Victor Okafor</t>
+  </si>
+  <si>
+    <t>victoro@example.com</t>
+  </si>
+  <si>
+    <t>victor1999</t>
+  </si>
+  <si>
+    <t>STU1034</t>
+  </si>
+  <si>
+    <t>victor.o@gmail.com</t>
+  </si>
+  <si>
+    <t>1999-11-05</t>
+  </si>
+  <si>
+    <t>7418529630</t>
+  </si>
+  <si>
+    <t>Nigerian</t>
+  </si>
+  <si>
+    <t>+234</t>
+  </si>
+  <si>
+    <t>Political Science</t>
+  </si>
+  <si>
+    <t>Maria Gonzalez</t>
+  </si>
+  <si>
+    <t>mariag@example.com</t>
+  </si>
+  <si>
+    <t>maria2001</t>
+  </si>
+  <si>
+    <t>STU1035</t>
+  </si>
+  <si>
+    <t>maria.g@gmail.com</t>
+  </si>
+  <si>
+    <t>2001-05-19</t>
+  </si>
+  <si>
+    <t>Mexican</t>
+  </si>
+  <si>
+    <t>+52</t>
+  </si>
+  <si>
+    <t>Journalism</t>
+  </si>
+  <si>
+    <t>Samuel Osei</t>
+  </si>
+  <si>
+    <t>samuelo@example.com</t>
+  </si>
+  <si>
+    <t>samuel2000</t>
+  </si>
+  <si>
+    <t>STU1036</t>
+  </si>
+  <si>
+    <t>samuel.o@gmail.com</t>
+  </si>
+  <si>
+    <t>2000-08-27</t>
+  </si>
+  <si>
+    <t>Ghanaian</t>
+  </si>
+  <si>
+    <t>+233</t>
+  </si>
+  <si>
+    <t>Sociology</t>
+  </si>
+  <si>
+    <t>Fiona MacLeod</t>
+  </si>
+  <si>
+    <t>fionam@example.com</t>
+  </si>
+  <si>
+    <t>fiona1997</t>
+  </si>
+  <si>
+    <t>STU1037</t>
+  </si>
+  <si>
+    <t>fiona.m@gmail.com</t>
+  </si>
+  <si>
+    <t>1997-10-13</t>
+  </si>
+  <si>
+    <t>Scottish</t>
+  </si>
+  <si>
+    <t>+44</t>
+  </si>
+  <si>
+    <t>History</t>
+  </si>
+  <si>
+    <t>Abdul Rahman</t>
+  </si>
+  <si>
+    <t>abdulr@example.com</t>
+  </si>
+  <si>
+    <t>abdul2002</t>
+  </si>
+  <si>
+    <t>STU1038</t>
+  </si>
+  <si>
+    <t>abdul.r@gmail.com</t>
+  </si>
+  <si>
+    <t>2002-12-11</t>
+  </si>
+  <si>
+    <t>UAE</t>
+  </si>
+  <si>
+    <t>+971</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Sophia Nguyen</t>
+  </si>
+  <si>
+    <t>sophian@example.com</t>
+  </si>
+  <si>
+    <t>sophia2001</t>
+  </si>
+  <si>
+    <t>STU1039</t>
+  </si>
+  <si>
+    <t>sophia.n@gmail.com</t>
+  </si>
+  <si>
+    <t>2001-04-05</t>
+  </si>
+  <si>
+    <t>Vietnamese</t>
+  </si>
+  <si>
+    <t>+84</t>
+  </si>
+  <si>
+    <t>Linguistics</t>
+  </si>
+  <si>
+    <t>Diego Hernandez</t>
+  </si>
+  <si>
+    <t>diegoh@example.com</t>
+  </si>
+  <si>
+    <t>diego1998</t>
+  </si>
+  <si>
+    <t>STU1040</t>
+  </si>
+  <si>
+    <t>diego.h@gmail.com</t>
+  </si>
+  <si>
+    <t>1998-06-23</t>
+  </si>
+  <si>
+    <t>Argentinian</t>
+  </si>
+  <si>
+    <t>+54</t>
+  </si>
+  <si>
+    <t>Sports Science</t>
+  </si>
+  <si>
+    <t>rollNo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -83,20 +779,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -107,23 +796,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:H31" totalsRowShown="0">
-  <autoFilter ref="A1:H31"/>
-  <tableColumns count="8">
-    <tableColumn id="2" name="email"/>
-    <tableColumn id="4" name="name"/>
-    <tableColumn id="5" name="collegeId"/>
-    <tableColumn id="6" name="college"/>
-    <tableColumn id="7" name="departmentId"/>
-    <tableColumn id="8" name="departmentId2" dataDxfId="0"/>
-    <tableColumn id="9" name="facultyId"/>
-    <tableColumn id="10" name="faculty"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -137,39 +809,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -204,7 +876,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -248,161 +920,210 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="26.44140625" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="17.77734375" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" customWidth="1"/>
-    <col min="6" max="6" width="20.21875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="21.77734375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -416,10 +1137,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -427,11 +1148,893 @@
       <c r="H1" t="s">
         <v>6</v>
       </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" t="s">
+        <v>68</v>
+      </c>
+      <c r="K7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" t="s">
+        <v>93</v>
+      </c>
+      <c r="H10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" t="s">
+        <v>102</v>
+      </c>
+      <c r="I11" t="s">
+        <v>103</v>
+      </c>
+      <c r="J11" t="s">
+        <v>104</v>
+      </c>
+      <c r="K11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" t="s">
+        <v>112</v>
+      </c>
+      <c r="I12" t="s">
+        <v>113</v>
+      </c>
+      <c r="J12" t="s">
+        <v>114</v>
+      </c>
+      <c r="K12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I13" t="s">
+        <v>123</v>
+      </c>
+      <c r="J13" t="s">
+        <v>124</v>
+      </c>
+      <c r="K13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" t="s">
+        <v>130</v>
+      </c>
+      <c r="G14" t="s">
+        <v>131</v>
+      </c>
+      <c r="H14" t="s">
+        <v>132</v>
+      </c>
+      <c r="I14" t="s">
+        <v>133</v>
+      </c>
+      <c r="J14" t="s">
+        <v>134</v>
+      </c>
+      <c r="K14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F15" t="s">
+        <v>140</v>
+      </c>
+      <c r="G15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H15" t="s">
+        <v>142</v>
+      </c>
+      <c r="I15" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16" t="s">
+        <v>147</v>
+      </c>
+      <c r="G16" t="s">
+        <v>148</v>
+      </c>
+      <c r="H16" t="s">
+        <v>149</v>
+      </c>
+      <c r="I16" t="s">
+        <v>150</v>
+      </c>
+      <c r="J16" t="s">
+        <v>151</v>
+      </c>
+      <c r="K16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>153</v>
+      </c>
+      <c r="B17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17">
+        <v>21</v>
+      </c>
+      <c r="E17" t="s">
+        <v>156</v>
+      </c>
+      <c r="F17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G17" t="s">
+        <v>158</v>
+      </c>
+      <c r="H17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I17" t="s">
+        <v>160</v>
+      </c>
+      <c r="J17" t="s">
+        <v>161</v>
+      </c>
+      <c r="K17" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" t="s">
+        <v>165</v>
+      </c>
+      <c r="D18">
+        <v>22</v>
+      </c>
+      <c r="E18" t="s">
+        <v>166</v>
+      </c>
+      <c r="F18" t="s">
+        <v>167</v>
+      </c>
+      <c r="G18" t="s">
+        <v>168</v>
+      </c>
+      <c r="H18" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" t="s">
+        <v>172</v>
+      </c>
+      <c r="D19">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>173</v>
+      </c>
+      <c r="F19" t="s">
+        <v>174</v>
+      </c>
+      <c r="G19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" t="s">
+        <v>176</v>
+      </c>
+      <c r="J19" t="s">
+        <v>177</v>
+      </c>
+      <c r="K19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>181</v>
+      </c>
+      <c r="F20" t="s">
+        <v>182</v>
+      </c>
+      <c r="G20" t="s">
+        <v>183</v>
+      </c>
+      <c r="H20" t="s">
+        <v>184</v>
+      </c>
+      <c r="I20" t="s">
+        <v>185</v>
+      </c>
+      <c r="J20" t="s">
+        <v>186</v>
+      </c>
+      <c r="K20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B21" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21">
+        <v>24</v>
+      </c>
+      <c r="E21" t="s">
+        <v>191</v>
+      </c>
+      <c r="F21" t="s">
+        <v>192</v>
+      </c>
+      <c r="G21" t="s">
+        <v>193</v>
+      </c>
+      <c r="H21" t="s">
+        <v>149</v>
+      </c>
+      <c r="I21" t="s">
+        <v>194</v>
+      </c>
+      <c r="J21" t="s">
+        <v>195</v>
+      </c>
+      <c r="K21" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" t="s">
+        <v>198</v>
+      </c>
+      <c r="C22" t="s">
+        <v>199</v>
+      </c>
+      <c r="D22">
+        <v>25</v>
+      </c>
+      <c r="E22" t="s">
+        <v>200</v>
+      </c>
+      <c r="F22" t="s">
+        <v>201</v>
+      </c>
+      <c r="G22" t="s">
+        <v>202</v>
+      </c>
+      <c r="H22" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" t="s">
+        <v>203</v>
+      </c>
+      <c r="J22" t="s">
+        <v>204</v>
+      </c>
+      <c r="K22" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>206</v>
+      </c>
+      <c r="B23" t="s">
+        <v>207</v>
+      </c>
+      <c r="C23" t="s">
+        <v>208</v>
+      </c>
+      <c r="D23">
+        <v>26</v>
+      </c>
+      <c r="E23" t="s">
+        <v>209</v>
+      </c>
+      <c r="F23" t="s">
+        <v>210</v>
+      </c>
+      <c r="G23" t="s">
+        <v>211</v>
+      </c>
+      <c r="H23" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" t="s">
+        <v>212</v>
+      </c>
+      <c r="J23" t="s">
+        <v>213</v>
+      </c>
+      <c r="K23" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>215</v>
+      </c>
+      <c r="B24" t="s">
+        <v>216</v>
+      </c>
+      <c r="C24" t="s">
+        <v>217</v>
+      </c>
+      <c r="D24">
+        <v>27</v>
+      </c>
+      <c r="E24" t="s">
+        <v>218</v>
+      </c>
+      <c r="F24" t="s">
+        <v>219</v>
+      </c>
+      <c r="G24" t="s">
+        <v>220</v>
+      </c>
+      <c r="H24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" t="s">
+        <v>221</v>
+      </c>
+      <c r="J24" t="s">
+        <v>222</v>
+      </c>
+      <c r="K24" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>224</v>
+      </c>
+      <c r="B25" t="s">
+        <v>225</v>
+      </c>
+      <c r="C25" t="s">
+        <v>226</v>
+      </c>
+      <c r="D25">
+        <v>28</v>
+      </c>
+      <c r="E25" t="s">
+        <v>227</v>
+      </c>
+      <c r="F25" t="s">
+        <v>228</v>
+      </c>
+      <c r="G25" t="s">
+        <v>229</v>
+      </c>
+      <c r="H25" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" t="s">
+        <v>230</v>
+      </c>
+      <c r="J25" t="s">
+        <v>231</v>
+      </c>
+      <c r="K25" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>233</v>
+      </c>
+      <c r="B26" t="s">
+        <v>234</v>
+      </c>
+      <c r="C26" t="s">
+        <v>235</v>
+      </c>
+      <c r="D26">
+        <v>29</v>
+      </c>
+      <c r="E26" t="s">
+        <v>236</v>
+      </c>
+      <c r="F26" t="s">
+        <v>237</v>
+      </c>
+      <c r="G26" t="s">
+        <v>238</v>
+      </c>
+      <c r="H26" t="s">
+        <v>66</v>
+      </c>
+      <c r="I26" t="s">
+        <v>239</v>
+      </c>
+      <c r="J26" t="s">
+        <v>240</v>
+      </c>
+      <c r="K26" t="s">
+        <v>241</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>